--- a/backend/income_details.xlsx
+++ b/backend/income_details.xlsx
@@ -415,16 +415,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Web Project</v>
+        <v>Web</v>
       </c>
       <c r="B2">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="C2" t="str">
         <v>Freelancing</v>
       </c>
       <c r="D2" t="str">
-        <v>9/2/2026</v>
+        <v>28/7/2026</v>
       </c>
     </row>
   </sheetData>
